--- a/input/old/Metadata _Check Vendor's Partners_SW_10_06_PF_VENDOR.xlsx
+++ b/input/old/Metadata _Check Vendor's Partners_SW_10_06_PF_VENDOR.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07.01.2026 at 16:54 by ILIYAR</t>
+          <t>07.01.2026 at 16:54 by REDACTED</t>
         </is>
       </c>
     </row>
